--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12416" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF8178F-5ED7-4CA5-A781-8E4FE32C097F}"/>
+  <xr:revisionPtr revIDLastSave="12418" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A2EF04F-D8E9-4907-9FFA-FBE9B6B44C20}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -7912,6 +7912,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9484,63 +9541,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -11043,88 +11043,84 @@
 </namedSheetViews>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J158" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J158" totalsRowShown="0" headerRowDxfId="152" dataDxfId="150" headerRowBorderDxfId="151" tableBorderDxfId="149" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J158" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J158">
     <sortCondition ref="A1:A158"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="144"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="BOM Qty Required" dataDxfId="143" dataCellStyle="Normal 7"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="142"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="141"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="140">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="148"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="147"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="BOM Qty Required" dataDxfId="146" dataCellStyle="Normal 7"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="145"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="144"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="143">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="139" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="138"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Size" dataDxfId="137" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="136"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="142" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="141"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Size" dataDxfId="140" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="139"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D54" totalsRowShown="0" headerRowDxfId="77" tableBorderDxfId="76" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D54" totalsRowShown="0" headerRowDxfId="80" tableBorderDxfId="79" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D54" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D54">
     <sortCondition ref="B1:B54"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="74" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="73" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D76" totalsRowShown="0" headerRowDxfId="71" tableBorderDxfId="70" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D76" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D76" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D76">
     <sortCondition ref="B1:B76"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="68" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="67" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:J112" totalsRowCount="1" headerRowDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:J112" totalsRowCount="1" headerRowDxfId="68">
   <autoFilter ref="A1:J111" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J111">
     <sortCondition ref="A1:A111"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" totalsRowLabel="Valkyrie V2" dataDxfId="64" totalsRowDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Normal 7"/>
-    <tableColumn id="7" xr3:uid="{D9E1579D-2958-49E6-9023-57D43052F87F}" name="Weight MT" totalsRowFunction="custom" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Normal 7">
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" totalsRowLabel="Valkyrie V2" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="65" totalsRowDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="63" totalsRowDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="60" totalsRowDxfId="59" dataCellStyle="Normal 7"/>
+    <tableColumn id="7" xr3:uid="{D9E1579D-2958-49E6-9023-57D43052F87F}" name="Weight MT" totalsRowFunction="custom" dataDxfId="58" totalsRowDxfId="57" dataCellStyle="Normal 7">
       <totalsRowFormula>SUBTOTAL(109,Table6[Weight MT])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight HT" totalsRowFunction="custom" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Normal 7">
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight HT" totalsRowFunction="custom" dataDxfId="56" totalsRowDxfId="55" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[Weight HT])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>$M$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="47" totalsRowDxfId="46">
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="49">
       <calculatedColumnFormula>Table6[[#This Row],[Time/item]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11133,39 +11129,39 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}" name="Table21" displayName="Table21" ref="A1:K115" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}" name="Table21" displayName="Table21" ref="A1:K115" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="A1:K115" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J115">
     <sortCondition ref="D1:D115"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{07401D67-326A-456C-83EE-6254807B759D}" name="Type" dataDxfId="43" dataCellStyle="Normal 13"/>
-    <tableColumn id="2" xr3:uid="{01841385-7AF0-4832-AD07-D9B6A289B738}" name="Device" dataDxfId="42" dataCellStyle="Normal 13"/>
-    <tableColumn id="3" xr3:uid="{4EBC60AB-DBDA-46AD-8145-0260DB456AC9}" name="Ident" dataDxfId="41" dataCellStyle="Normal 13"/>
-    <tableColumn id="4" xr3:uid="{27974694-306B-43D4-9D9F-3BC67D1A167D}" name="Connector" dataDxfId="40" dataCellStyle="Normal 13"/>
-    <tableColumn id="5" xr3:uid="{247A2715-9549-43E9-BC8D-C5AF905911E6}" name="From Pin" dataDxfId="39" dataCellStyle="Normal 13"/>
-    <tableColumn id="6" xr3:uid="{CAED148B-51FF-46DC-A56B-A5F88498E2F4}" name="Wire size AWG" dataDxfId="38" dataCellStyle="Normal 13"/>
-    <tableColumn id="7" xr3:uid="{A8E15565-9D43-4F89-9D4B-714FAEED327C}" name="Color" dataDxfId="37" dataCellStyle="Normal 13"/>
-    <tableColumn id="8" xr3:uid="{EF11CEA0-492E-4C41-811D-955E5C409484}" name="Length mm" dataDxfId="36" dataCellStyle="Normal 13"/>
-    <tableColumn id="9" xr3:uid="{B64154E3-1929-4FEB-B7E7-B1FCB2AE49D2}" name="To pin" dataDxfId="35" dataCellStyle="Normal 13"/>
-    <tableColumn id="10" xr3:uid="{1768166D-BE53-4B2E-9459-10942122F8E6}" name="Comment" dataDxfId="34" dataCellStyle="Normal 13"/>
-    <tableColumn id="11" xr3:uid="{05B1D6FD-1EF2-4ED9-B65F-34786822ECAB}" name="SLEEVE" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{07401D67-326A-456C-83EE-6254807B759D}" name="Type" dataDxfId="46" dataCellStyle="Normal 13"/>
+    <tableColumn id="2" xr3:uid="{01841385-7AF0-4832-AD07-D9B6A289B738}" name="Device" dataDxfId="45" dataCellStyle="Normal 13"/>
+    <tableColumn id="3" xr3:uid="{4EBC60AB-DBDA-46AD-8145-0260DB456AC9}" name="Ident" dataDxfId="44" dataCellStyle="Normal 13"/>
+    <tableColumn id="4" xr3:uid="{27974694-306B-43D4-9D9F-3BC67D1A167D}" name="Connector" dataDxfId="43" dataCellStyle="Normal 13"/>
+    <tableColumn id="5" xr3:uid="{247A2715-9549-43E9-BC8D-C5AF905911E6}" name="From Pin" dataDxfId="42" dataCellStyle="Normal 13"/>
+    <tableColumn id="6" xr3:uid="{CAED148B-51FF-46DC-A56B-A5F88498E2F4}" name="Wire size AWG" dataDxfId="41" dataCellStyle="Normal 13"/>
+    <tableColumn id="7" xr3:uid="{A8E15565-9D43-4F89-9D4B-714FAEED327C}" name="Color" dataDxfId="40" dataCellStyle="Normal 13"/>
+    <tableColumn id="8" xr3:uid="{EF11CEA0-492E-4C41-811D-955E5C409484}" name="Length mm" dataDxfId="39" dataCellStyle="Normal 13"/>
+    <tableColumn id="9" xr3:uid="{B64154E3-1929-4FEB-B7E7-B1FCB2AE49D2}" name="To pin" dataDxfId="38" dataCellStyle="Normal 13"/>
+    <tableColumn id="10" xr3:uid="{1768166D-BE53-4B2E-9459-10942122F8E6}" name="Comment" dataDxfId="37" dataCellStyle="Normal 13"/>
+    <tableColumn id="11" xr3:uid="{05B1D6FD-1EF2-4ED9-B65F-34786822ECAB}" name="SLEEVE" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{824DC2E7-B869-4223-8CA0-8BB231246BE6}" name="Table43" displayName="Table43" ref="A4:G31" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{824DC2E7-B869-4223-8CA0-8BB231246BE6}" name="Table43" displayName="Table43" ref="A4:G31" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34">
   <autoFilter ref="A4:G31" xr:uid="{9F2F2CC6-19FD-46E3-8A6D-884FD4A96CE0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AE39532B-D989-4297-B014-612247804D38}" name="Type" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{299576E6-0ACD-495A-89C7-26F593973C04}" name="Component" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{25D583BA-BC0F-45C1-8195-BA00EEE7001D}" name="Pin" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{07FBDE4D-2555-4C8A-8314-D8A735D09CA9}" name="AWG" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{C8C1F170-B800-45DE-8C38-42F23A1A89F1}" name="Wire Colour" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{7E640059-24DB-480D-83B2-FC35DE245721}" name="Wire Length mm" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{7C27CE98-27C4-49E7-9D13-ADA6DCAD2043}" name="Device/Pin" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{AE39532B-D989-4297-B014-612247804D38}" name="Type" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{299576E6-0ACD-495A-89C7-26F593973C04}" name="Component" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{25D583BA-BC0F-45C1-8195-BA00EEE7001D}" name="Pin" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{07FBDE4D-2555-4C8A-8314-D8A735D09CA9}" name="AWG" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{C8C1F170-B800-45DE-8C38-42F23A1A89F1}" name="Wire Colour" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{7E640059-24DB-480D-83B2-FC35DE245721}" name="Wire Length mm" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{7C27CE98-27C4-49E7-9D13-ADA6DCAD2043}" name="Device/Pin" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11178,7 +11174,7 @@
     <sortCondition ref="A1:A13"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="152"/>
+    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="25"/>
     <tableColumn id="1" xr3:uid="{E1FF070C-6993-4332-802B-B4D29E1606E7}" name="Function"/>
     <tableColumn id="3" xr3:uid="{8FBB1689-4854-43C5-AC93-F6E571CF242D}" name="Description"/>
   </tableColumns>
@@ -11193,8 +11189,8 @@
     <sortCondition ref="A16:A30"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="151"/>
-    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="150"/>
+    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="23"/>
     <tableColumn id="3" xr3:uid="{5B376876-1002-41A2-9B1B-97FBB74534E9}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -11250,16 +11246,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="135" dataDxfId="134" tableBorderDxfId="133" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137" tableBorderDxfId="136" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="132"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="131"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="130" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="129"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="135"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="134"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="133" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11293,105 +11289,105 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D47" totalsRowShown="0" headerRowDxfId="128" tableBorderDxfId="127" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D47" totalsRowShown="0" headerRowDxfId="131" tableBorderDxfId="130" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D47" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D47">
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="126" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="125" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="124" totalsRowDxfId="123" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="129" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="128" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="127" totalsRowDxfId="126" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D59" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121" tableBorderDxfId="120" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D59" totalsRowShown="0" headerRowDxfId="125" dataDxfId="124" tableBorderDxfId="123" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D59" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D59">
     <sortCondition ref="B1:B59"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="119" totalsRowDxfId="118" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="117" totalsRowDxfId="116" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="115" totalsRowDxfId="114" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="122" totalsRowDxfId="121" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="120" totalsRowDxfId="119" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="118" totalsRowDxfId="117" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D33" totalsRowShown="0" headerRowDxfId="113" dataDxfId="112" tableBorderDxfId="111" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D33" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115" tableBorderDxfId="114" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D33" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D33">
     <sortCondition ref="B1:B33"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="110" totalsRowDxfId="109" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="108" totalsRowDxfId="107" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="106" totalsRowDxfId="105" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="113" totalsRowDxfId="112" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="111" totalsRowDxfId="110" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="109" totalsRowDxfId="108" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B35:D44" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103" tableBorderDxfId="102" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B35:D44" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106" tableBorderDxfId="105" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B35:D44" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B36:D44">
     <sortCondition ref="B35:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="101" totalsRowDxfId="100" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="99" totalsRowDxfId="98" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="97" totalsRowDxfId="96" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="104" totalsRowDxfId="103" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="102" totalsRowDxfId="101" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="100" totalsRowDxfId="99" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D68" totalsRowShown="0" headerRowDxfId="95" tableBorderDxfId="94" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D68" totalsRowShown="0" headerRowDxfId="98" tableBorderDxfId="97" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D68" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D68">
     <sortCondition ref="B1:B68"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="93" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="92" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="91" totalsRowDxfId="90" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="96" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="95" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="94" totalsRowDxfId="93" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D11" totalsRowShown="0" headerRowDxfId="89" tableBorderDxfId="88" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D11" totalsRowShown="0" headerRowDxfId="92" tableBorderDxfId="91" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D11" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D11">
     <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="87" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="86" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="85" totalsRowDxfId="84" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="90" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="89" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="88" totalsRowDxfId="87" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A7720F7C-DDE4-480A-9200-E1A2AB06F106}" name="Table9131718192024" displayName="Table9131718192024" ref="B1:D12" totalsRowShown="0" headerRowDxfId="83" tableBorderDxfId="82" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A7720F7C-DDE4-480A-9200-E1A2AB06F106}" name="Table9131718192024" displayName="Table9131718192024" ref="B1:D12" totalsRowShown="0" headerRowDxfId="86" tableBorderDxfId="85" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D12" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D12">
     <sortCondition ref="B1:B12"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DE5B6A3D-F02B-442F-8F0E-2D97466E9D55}" name="Part name" totalsRowDxfId="81" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{CD84E571-7957-4B8F-9F34-DA3FA6BF0E23}" name="Description" totalsRowDxfId="80" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="79" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{DE5B6A3D-F02B-442F-8F0E-2D97466E9D55}" name="Part name" totalsRowDxfId="84" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{CD84E571-7957-4B8F-9F34-DA3FA6BF0E23}" name="Description" totalsRowDxfId="83" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="82" totalsRowDxfId="81" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
